--- a/程序/PCA数据.xlsx
+++ b/程序/PCA数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\大论文\需水预测\PSO-BP神经网络回归预测模型（粒子群算法优化BP神经网络）\程序\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225961DA-C0FD-4CDB-8B3E-29CC8868536F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D884F-B63D-4F6F-9D86-066A5239DE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="28605" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>常住人口</t>
   </si>
@@ -346,14 +346,6 @@
       <t/>
     </r>
   </si>
-  <si>
-    <t>需水量（前一年）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需水量差分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -362,7 +354,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,13 +434,6 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="1"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -491,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -545,9 +530,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -830,14 +812,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultColWidth="13.125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="31.5" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="13.125" style="1"/>
+    <col min="1" max="5" width="31.5" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="13.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>48</v>
       </c>
@@ -853,463 +835,355 @@
       <c r="E1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
         <v>3145.13</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="1">
         <v>1399.92</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="1">
         <v>4601.3999999999996</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="1">
         <v>490.30188358599111</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="1">
         <v>30.073714780374061</v>
       </c>
-      <c r="F2" s="7">
-        <v>-2.1138240751920421</v>
-      </c>
-      <c r="G2" s="7">
-        <v>188.30948032558243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>3111</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="1">
         <v>3745.19</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="1">
         <v>4601</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="1">
         <v>482.95943173327476</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="1">
         <v>28.565593390207813</v>
       </c>
-      <c r="F3" s="7">
-        <v>9.5659496284114027</v>
-      </c>
-      <c r="G3" s="7">
-        <v>186.19565625039039</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>3076.87</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="1">
         <v>4450</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="1">
         <v>4459.5</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="1">
         <v>475.61697988055846</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="1">
         <v>27.05747200004156</v>
       </c>
-      <c r="F4" s="7">
-        <v>4.2634756770822548</v>
-      </c>
-      <c r="G4" s="7">
-        <v>195.76160587880179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>3042.77</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="1">
         <v>5287.57</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="1">
         <v>4460</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="1">
         <v>468.27452802784217</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="1">
         <v>25.549350609875308</v>
       </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>200.02508155588404</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>3023.97</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="1">
         <v>6346.29</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="1">
         <v>4556</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="1">
         <v>460.93207617512587</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="1">
         <v>24.041229219709059</v>
       </c>
-      <c r="F6" s="7">
-        <v>-3.2603049295334472</v>
-      </c>
-      <c r="G6" s="7">
-        <v>200.02508155588404</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>3015.02</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="1">
         <v>7196.89</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="1">
         <v>4601.2</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="1">
         <v>453.58962432240952</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="1">
         <v>22.533107829542807</v>
       </c>
-      <c r="F7" s="7">
-        <v>-5.4647766263505844</v>
-      </c>
-      <c r="G7" s="7">
-        <v>196.7647766263506</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>2977</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="1">
         <v>8920.3700000000008</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="1">
         <v>4660.6000000000004</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="1">
         <v>447</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="1">
         <v>30</v>
       </c>
-      <c r="F8" s="7">
-        <v>1.0999999999999943</v>
-      </c>
-      <c r="G8" s="7">
-        <v>191.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>2956.6</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="1">
         <v>10744.32</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="1">
         <v>4696.7</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="1">
         <v>442</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="1">
         <v>27</v>
       </c>
-      <c r="F9" s="7">
-        <v>-2.9000000000000057</v>
-      </c>
-      <c r="G9" s="7">
-        <v>192.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>2943.7300000000005</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="1">
         <v>12182.94</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="1">
         <v>4706.1000000000004</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="1">
         <v>397</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="1">
         <v>20</v>
       </c>
-      <c r="F10" s="7">
-        <v>-1.9000000000000057</v>
-      </c>
-      <c r="G10" s="7">
-        <v>189.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>2940.49</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="1">
         <v>13558.880000000001</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="1">
         <v>4720.59</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="1">
         <v>417</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="1">
         <v>21.4</v>
       </c>
-      <c r="F11" s="7">
-        <v>3.3000000000000114</v>
-      </c>
-      <c r="G11" s="7">
-        <v>187.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>2952.06</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="1">
         <v>15151.490000000002</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="1">
         <v>4710.49</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="1">
         <v>405.4</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="1">
         <v>18.899999999999999</v>
       </c>
-      <c r="F12" s="7">
-        <v>-6.3000000000000114</v>
-      </c>
-      <c r="G12" s="7">
-        <v>190.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>2957.9</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="1">
         <v>16564.3</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="1">
         <v>4728.88</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="1">
         <v>388.7</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="1">
         <v>18.100000000000001</v>
       </c>
-      <c r="F13" s="7">
-        <v>3.3000000000000114</v>
-      </c>
-      <c r="G13" s="7">
-        <v>184.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>2970.15</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="1">
         <v>18160.2</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="1">
         <v>4701.5099999999993</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="1">
         <v>430.5</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="1">
         <v>14.2</v>
       </c>
-      <c r="F14" s="7">
-        <v>3.2999999999999829</v>
-      </c>
-      <c r="G14" s="7">
-        <v>187.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>2987.39</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="1">
         <v>20268.769999999997</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="1">
         <v>4663.7299999999996</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="1">
         <v>443.3</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="1">
         <v>16.2</v>
       </c>
-      <c r="F15" s="7">
-        <v>-26.321722135020877</v>
-      </c>
-      <c r="G15" s="7">
-        <v>191.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>2992.03</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="1">
         <v>21365.980000000003</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="1">
         <v>4713.7700000000004</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="1">
         <v>414.46208484411858</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="1">
         <v>30.33985384922693</v>
       </c>
-      <c r="F16" s="7">
-        <v>11.894738863792497</v>
-      </c>
-      <c r="G16" s="7">
-        <v>164.87827786497911</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>2997.58</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="1">
         <v>22963.34</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="1">
         <v>4717.45</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="1">
         <v>458.61340716900486</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="1">
         <v>28.743019436109719</v>
       </c>
-      <c r="F17" s="7">
-        <v>-9.8730167287716029</v>
-      </c>
-      <c r="G17" s="7">
-        <v>176.77301672877161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>2994.2900000000004</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="1">
         <v>23837.96</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="1">
         <v>4758.7700000000004</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="1">
         <v>391.8</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="1">
         <v>11.7</v>
       </c>
-      <c r="F18" s="7">
-        <v>-2.4000000000000057</v>
-      </c>
-      <c r="G18" s="7">
-        <v>166.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>2990.47</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="1">
         <v>26731.89</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="1">
         <v>4768</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="1">
         <v>381.71088513266028</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="1">
         <v>17.21032645248545</v>
       </c>
-      <c r="F19" s="7">
-        <v>29.800000000000011</v>
-      </c>
-      <c r="G19" s="7">
-        <v>164.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>2983.71</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="1">
         <v>28397.05</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="1">
         <v>4783.75</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="1">
         <v>459.96596408924211</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="1">
         <v>15.790918085270157</v>
       </c>
-      <c r="F20" s="7">
-        <v>-29.300000000000011</v>
-      </c>
-      <c r="G20" s="18">
-        <v>194.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:7" ht="20.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>2981.85</v>
+      </c>
+      <c r="B21" s="1">
+        <v>30081.05</v>
+      </c>
+      <c r="C21" s="1">
+        <v>4799.0600000000004</v>
+      </c>
+      <c r="D21" s="1">
+        <v>386.63805677066728</v>
+      </c>
+      <c r="E21" s="1">
+        <v>15.7022050623192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>4</v>
       </c>
@@ -1325,10 +1199,8 @@
       <c r="E114" s="2">
         <v>4</v>
       </c>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>5</v>
       </c>
@@ -1344,10 +1216,8 @@
       <c r="E115" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>6</v>
       </c>
@@ -1363,10 +1233,8 @@
       <c r="E116" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>7</v>
       </c>
@@ -1382,10 +1250,8 @@
       <c r="E117" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>8</v>
       </c>
@@ -1401,10 +1267,8 @@
       <c r="E118" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>9</v>
       </c>
@@ -1420,10 +1284,8 @@
       <c r="E119" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>10</v>
       </c>
@@ -1439,10 +1301,8 @@
       <c r="E120" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>11</v>
       </c>
@@ -1458,46 +1318,36 @@
       <c r="E121" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>4</v>
       </c>
@@ -1513,10 +1363,8 @@
       <c r="E126" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>1</v>
       </c>
@@ -1532,10 +1380,8 @@
       <c r="E127" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>2</v>
       </c>
@@ -1551,10 +1397,8 @@
       <c r="E128" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>3</v>
       </c>
@@ -1570,10 +1414,8 @@
       <c r="E129" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>4</v>
       </c>
@@ -1589,10 +1431,8 @@
       <c r="E130" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>5</v>
       </c>
@@ -1608,10 +1448,8 @@
       <c r="E131" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>6</v>
       </c>
@@ -1627,10 +1465,8 @@
       <c r="E132" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>7</v>
       </c>
@@ -1646,10 +1482,8 @@
       <c r="E133" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>8</v>
       </c>
@@ -1665,10 +1499,8 @@
       <c r="E134" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>9</v>
       </c>
@@ -1684,8 +1516,6 @@
       <c r="E135" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
